--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,32 +1,280 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="323" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{098DA5F3-A63C-48E1-BE73-F5470625A2FE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DWM" sheetId="4" r:id="rId1"/>
+    <sheet name="Phases" sheetId="1" r:id="rId2"/>
+    <sheet name="Project Timeline" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+  <si>
+    <t>Pilot : Tradesphere</t>
+  </si>
+  <si>
+    <t>Tradesphere Project Tracker</t>
+  </si>
+  <si>
+    <t>Task ID</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Task Name</t>
+  </si>
+  <si>
+    <t>Dependency Task ID</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Duration (Days)</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Requirement Analysis &amp; Solution Design</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Phase 3</t>
+  </si>
+  <si>
+    <t>Database Design &amp; Architecture Setup</t>
+  </si>
+  <si>
+    <t>In-progress</t>
+  </si>
+  <si>
+    <t>In-Progress</t>
+  </si>
+  <si>
+    <t>Phase 4</t>
+  </si>
+  <si>
+    <t>Phase 5</t>
+  </si>
+  <si>
+    <t>Phase 6</t>
+  </si>
+  <si>
+    <t>Phase 7</t>
+  </si>
+  <si>
+    <t>Phase 8</t>
+  </si>
+  <si>
+    <t>Phase 9</t>
+  </si>
+  <si>
+    <t>Phase 10</t>
+  </si>
+  <si>
+    <t>Phase 11</t>
+  </si>
+  <si>
+    <t>Phase 12</t>
+  </si>
+  <si>
+    <t>Phase 13</t>
+  </si>
+  <si>
+    <t>Phase 14</t>
+  </si>
+  <si>
+    <t>Phase 15</t>
+  </si>
+  <si>
+    <t>Phase 16</t>
+  </si>
+  <si>
+    <t>Phase 17</t>
+  </si>
+  <si>
+    <t>Dependency (Task ID)</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Project Kickoff</t>
+  </si>
+  <si>
+    <t>08-06-2026</t>
+  </si>
+  <si>
+    <t>Requirement Gathering</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Solution Design</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Development Phase 1</t>
+  </si>
+  <si>
+    <t>Development Phase 2</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>System Testing</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>User Acceptance Testing</t>
+  </si>
+  <si>
+    <t>Go-Live</t>
+  </si>
+  <si>
+    <t>Production Deployment</t>
+  </si>
+  <si>
+    <t>Beats &amp; Beat Assignment Module</t>
+  </si>
+  <si>
+    <t>Authentication Module</t>
+  </si>
+  <si>
+    <t>Security Module</t>
+  </si>
+  <si>
+    <t>Employee Module</t>
+  </si>
+  <si>
+    <t>Territory Module</t>
+  </si>
+  <si>
+    <t>Promoter Module</t>
+  </si>
+  <si>
+    <t>Retailer Module</t>
+  </si>
+  <si>
+    <t>Attendance And EOD Module</t>
+  </si>
+  <si>
+    <t>Visit Module</t>
+  </si>
+  <si>
+    <t>Product Module</t>
+  </si>
+  <si>
+    <t>Retailer Stock Management</t>
+  </si>
+  <si>
+    <t>Order Module</t>
+  </si>
+  <si>
+    <t>UI/UX Design(Portal + App)</t>
+  </si>
+  <si>
+    <t>Dashboard &amp; Reporting</t>
+  </si>
+  <si>
+    <t>Phase 18</t>
+  </si>
+  <si>
+    <t>Testing, Bug fixing</t>
+  </si>
+  <si>
+    <t>Phase 19</t>
+  </si>
+  <si>
+    <t>Deployment And Go-live Suppot</t>
+  </si>
+  <si>
+    <t>Retailer Feedback Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Final date :- 31-Oct-26</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,10 +285,49 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -49,13 +336,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +405,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +673,931 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9">
+        <v>46181</v>
+      </c>
+      <c r="F3" s="3">
+        <v>7</v>
+      </c>
+      <c r="G3" s="10">
+        <f>E3+F3</f>
+        <v>46188</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="P3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9">
+        <f>G3+1</f>
+        <v>46189</v>
+      </c>
+      <c r="F4" s="3">
+        <v>14</v>
+      </c>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G21" si="0">E4+F4</f>
+        <v>46203</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9">
+        <f>G4+1</f>
+        <v>46204</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" ref="E6:E20" si="1">G5+1</f>
+        <v>46210</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="0"/>
+        <v>46215</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="1"/>
+        <v>46216</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="0"/>
+        <v>46221</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>46227</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="1"/>
+        <v>46228</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="0"/>
+        <v>46233</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="1"/>
+        <v>46234</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="0"/>
+        <v>46242</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="3">
+        <v>9</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="1"/>
+        <v>46243</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="0"/>
+        <v>46248</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="3">
+        <v>10</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="1"/>
+        <v>46249</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="0"/>
+        <v>46256</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="3">
+        <v>11</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="1"/>
+        <v>46257</v>
+      </c>
+      <c r="F13" s="3">
+        <v>7</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="0"/>
+        <v>46264</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="3">
+        <v>12</v>
+      </c>
+      <c r="E14" s="9">
+        <f t="shared" si="1"/>
+        <v>46265</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="0"/>
+        <v>46268</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="3">
+        <v>13</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="1"/>
+        <v>46269</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="0"/>
+        <v>46272</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="3">
+        <v>14</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="1"/>
+        <v>46273</v>
+      </c>
+      <c r="F16" s="3">
+        <v>7</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="0"/>
+        <v>46280</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="3">
+        <v>15</v>
+      </c>
+      <c r="E17" s="9">
+        <f t="shared" si="1"/>
+        <v>46281</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="0"/>
+        <v>46286</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="3">
+        <v>16</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="1"/>
+        <v>46287</v>
+      </c>
+      <c r="F18" s="3">
+        <v>15</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" si="0"/>
+        <v>46302</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="3">
+        <v>17</v>
+      </c>
+      <c r="E19" s="9">
+        <f t="shared" si="1"/>
+        <v>46303</v>
+      </c>
+      <c r="F19" s="3">
+        <v>7</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" si="0"/>
+        <v>46310</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="3">
+        <v>18</v>
+      </c>
+      <c r="E20" s="9">
+        <f>G19+1</f>
+        <v>46311</v>
+      </c>
+      <c r="F20" s="3">
+        <v>7</v>
+      </c>
+      <c r="G20" s="10">
+        <f t="shared" si="0"/>
+        <v>46318</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="3">
+        <v>19</v>
+      </c>
+      <c r="E21" s="9">
+        <f>G20+1</f>
+        <v>46319</v>
+      </c>
+      <c r="F21" s="3">
+        <v>7</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="0"/>
+        <v>46326</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C23" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H3:H21">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>$P$5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>$P$3</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>$P$4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="323" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{098DA5F3-A63C-48E1-BE73-F5470625A2FE}"/>
+  <xr:revisionPtr revIDLastSave="399" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8317B7A6-5347-40B4-8672-8C5CE52D8653}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>weekend off included</t>
+  </si>
+  <si>
     <t>Phase 1</t>
   </si>
   <si>
@@ -79,19 +82,25 @@
     <t>Completed</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Phase 2</t>
   </si>
   <si>
+    <t>Database Design &amp; Architecture Setup</t>
+  </si>
+  <si>
+    <t>In-progress</t>
+  </si>
+  <si>
     <t>Not Started</t>
   </si>
   <si>
     <t>Phase 3</t>
   </si>
   <si>
-    <t>Database Design &amp; Architecture Setup</t>
-  </si>
-  <si>
-    <t>In-progress</t>
+    <t>Authentication Module</t>
   </si>
   <si>
     <t>In-Progress</t>
@@ -100,45 +109,102 @@
     <t>Phase 4</t>
   </si>
   <si>
+    <t>Security Module</t>
+  </si>
+  <si>
     <t>Phase 5</t>
   </si>
   <si>
+    <t>Employee Module</t>
+  </si>
+  <si>
     <t>Phase 6</t>
   </si>
   <si>
+    <t>Territory Module</t>
+  </si>
+  <si>
     <t>Phase 7</t>
   </si>
   <si>
+    <t>Promoter Module</t>
+  </si>
+  <si>
     <t>Phase 8</t>
   </si>
   <si>
+    <t>Beats &amp; Beat Assignment Module</t>
+  </si>
+  <si>
     <t>Phase 9</t>
   </si>
   <si>
+    <t>Retailer Module</t>
+  </si>
+  <si>
     <t>Phase 10</t>
   </si>
   <si>
+    <t>Attendance And EOD Module</t>
+  </si>
+  <si>
     <t>Phase 11</t>
   </si>
   <si>
+    <t>Visit Module</t>
+  </si>
+  <si>
     <t>Phase 12</t>
   </si>
   <si>
+    <t>Retailer Feedback Module</t>
+  </si>
+  <si>
     <t>Phase 13</t>
   </si>
   <si>
+    <t>Product Module</t>
+  </si>
+  <si>
     <t>Phase 14</t>
   </si>
   <si>
+    <t>Retailer Stock Management</t>
+  </si>
+  <si>
     <t>Phase 15</t>
   </si>
   <si>
+    <t>Order Module</t>
+  </si>
+  <si>
     <t>Phase 16</t>
   </si>
   <si>
+    <t>UI/UX Design(Portal + App)</t>
+  </si>
+  <si>
     <t>Phase 17</t>
   </si>
   <si>
+    <t>Dashboard &amp; Reporting</t>
+  </si>
+  <si>
+    <t>Phase 18</t>
+  </si>
+  <si>
+    <t>Testing, Bug fixing</t>
+  </si>
+  <si>
+    <t>Phase 19</t>
+  </si>
+  <si>
+    <t>Deployment And Go-live Suppot</t>
+  </si>
+  <si>
+    <t>Final Date</t>
+  </si>
+  <si>
     <t>Dependency (Task ID)</t>
   </si>
   <si>
@@ -185,66 +251,6 @@
   </si>
   <si>
     <t>Production Deployment</t>
-  </si>
-  <si>
-    <t>Beats &amp; Beat Assignment Module</t>
-  </si>
-  <si>
-    <t>Authentication Module</t>
-  </si>
-  <si>
-    <t>Security Module</t>
-  </si>
-  <si>
-    <t>Employee Module</t>
-  </si>
-  <si>
-    <t>Territory Module</t>
-  </si>
-  <si>
-    <t>Promoter Module</t>
-  </si>
-  <si>
-    <t>Retailer Module</t>
-  </si>
-  <si>
-    <t>Attendance And EOD Module</t>
-  </si>
-  <si>
-    <t>Visit Module</t>
-  </si>
-  <si>
-    <t>Product Module</t>
-  </si>
-  <si>
-    <t>Retailer Stock Management</t>
-  </si>
-  <si>
-    <t>Order Module</t>
-  </si>
-  <si>
-    <t>UI/UX Design(Portal + App)</t>
-  </si>
-  <si>
-    <t>Dashboard &amp; Reporting</t>
-  </si>
-  <si>
-    <t>Phase 18</t>
-  </si>
-  <si>
-    <t>Testing, Bug fixing</t>
-  </si>
-  <si>
-    <t>Phase 19</t>
-  </si>
-  <si>
-    <t>Deployment And Go-live Suppot</t>
-  </si>
-  <si>
-    <t>Retailer Feedback Module</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Final date :- 31-Oct-26</t>
   </si>
 </sst>
 </file>
@@ -255,7 +261,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,15 +283,21 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -332,11 +344,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -353,12 +378,21 @@
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,10 +439,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -675,137 +705,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
   <dimension ref="A1:A34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1">
       <c r="A2" s="6">
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1">
       <c r="A3" s="6">
         <v>46175</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1">
       <c r="A4" s="6">
         <v>46176</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1">
       <c r="A5" s="6">
         <v>46177</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1">
       <c r="A6" s="6">
         <v>46178</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1">
       <c r="A7" s="6">
         <v>46179</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1">
       <c r="A8" s="6">
         <v>46180</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1">
       <c r="A9" s="6">
         <v>46181</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1">
       <c r="A10" s="6">
         <v>46182</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1">
       <c r="A11" s="6">
         <v>46183</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1">
       <c r="A12" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1">
       <c r="A13" s="6">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1">
       <c r="A15" s="6"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1">
       <c r="A16" s="6"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1">
       <c r="A17" s="6"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1">
       <c r="A18" s="6"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1">
       <c r="A19" s="6"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1">
       <c r="A23" s="6"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1">
       <c r="A24" s="6"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1">
       <c r="A25" s="6"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1">
       <c r="A26" s="6"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1">
       <c r="A27" s="6"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1">
       <c r="A28" s="6"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1">
       <c r="A29" s="6"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1">
       <c r="A30" s="6"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1">
       <c r="A31" s="6"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1">
       <c r="A32" s="6"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1">
       <c r="A33" s="6"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1">
       <c r="A34" s="6"/>
     </row>
   </sheetData>
@@ -816,18 +846,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
       <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
@@ -836,7 +867,7 @@
       <c r="E1" s="11"/>
       <c r="F1" s="11"/>
     </row>
-    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="30.75">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -855,557 +886,619 @@
       <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I2" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="9">
         <v>46181</v>
       </c>
       <c r="F3" s="3">
-        <v>7</v>
-      </c>
-      <c r="G3" s="10">
+        <v>9</v>
+      </c>
+      <c r="G3" s="16">
         <f>E3+F3</f>
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="J3" s="2"/>
       <c r="P3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="9">
         <f>G3+1</f>
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="F4" s="3">
-        <v>14</v>
-      </c>
-      <c r="G4" s="10">
+        <v>18</v>
+      </c>
+      <c r="G4" s="16">
         <f t="shared" ref="G4:G21" si="0">E4+F4</f>
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="14" t="s">
+        <v>14</v>
+      </c>
       <c r="P4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="9">
         <f>G4+1</f>
-        <v>46204</v>
+        <v>46210</v>
       </c>
       <c r="F5" s="3">
-        <v>5</v>
-      </c>
-      <c r="G5" s="10">
+        <v>7</v>
+      </c>
+      <c r="G5" s="16">
         <f t="shared" si="0"/>
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="P5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="9">
-        <f t="shared" ref="E6:E20" si="1">G5+1</f>
-        <v>46210</v>
+        <f t="shared" ref="E6:E19" si="1">G5+1</f>
+        <v>46218</v>
       </c>
       <c r="F6" s="3">
-        <v>5</v>
-      </c>
-      <c r="G6" s="10">
+        <v>2</v>
+      </c>
+      <c r="G6" s="16">
         <f t="shared" si="0"/>
-        <v>46215</v>
+        <v>46220</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I6" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="1"/>
-        <v>46216</v>
+        <v>46221</v>
       </c>
       <c r="F7" s="3">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10">
+        <v>7</v>
+      </c>
+      <c r="G7" s="16">
         <f t="shared" si="0"/>
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="1"/>
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="F8" s="3">
-        <v>5</v>
-      </c>
-      <c r="G8" s="10">
+        <v>7</v>
+      </c>
+      <c r="G8" s="16">
         <f t="shared" si="0"/>
-        <v>46227</v>
+        <v>46236</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="1"/>
-        <v>46228</v>
+        <v>46237</v>
       </c>
       <c r="F9" s="3">
-        <v>5</v>
-      </c>
-      <c r="G9" s="10">
+        <v>7</v>
+      </c>
+      <c r="G9" s="16">
         <f t="shared" si="0"/>
-        <v>46233</v>
+        <v>46244</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="1"/>
-        <v>46234</v>
+        <v>46245</v>
       </c>
       <c r="F10" s="3">
-        <v>8</v>
-      </c>
-      <c r="G10" s="10">
+        <v>10</v>
+      </c>
+      <c r="G10" s="16">
         <f t="shared" si="0"/>
-        <v>46242</v>
+        <v>46255</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" si="1"/>
-        <v>46243</v>
+        <v>46256</v>
       </c>
       <c r="F11" s="3">
-        <v>5</v>
-      </c>
-      <c r="G11" s="10">
+        <v>7</v>
+      </c>
+      <c r="G11" s="16">
         <f t="shared" si="0"/>
-        <v>46248</v>
+        <v>46263</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="1"/>
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="F12" s="3">
-        <v>7</v>
-      </c>
-      <c r="G12" s="10">
+        <v>9</v>
+      </c>
+      <c r="G12" s="16">
         <f t="shared" si="0"/>
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D13" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="1"/>
-        <v>46257</v>
+        <v>46274</v>
       </c>
       <c r="F13" s="3">
-        <v>7</v>
-      </c>
-      <c r="G13" s="10">
+        <v>9</v>
+      </c>
+      <c r="G13" s="16">
         <f t="shared" si="0"/>
-        <v>46264</v>
+        <v>46283</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D14" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="1"/>
-        <v>46265</v>
+        <v>46284</v>
       </c>
       <c r="F14" s="3">
-        <v>3</v>
-      </c>
-      <c r="G14" s="10">
+        <v>5</v>
+      </c>
+      <c r="G14" s="16">
         <f t="shared" si="0"/>
-        <v>46268</v>
+        <v>46289</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="1"/>
-        <v>46269</v>
+        <v>46290</v>
       </c>
       <c r="F15" s="3">
-        <v>3</v>
-      </c>
-      <c r="G15" s="10">
+        <v>5</v>
+      </c>
+      <c r="G15" s="16">
         <f t="shared" si="0"/>
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="1"/>
-        <v>46273</v>
+        <v>46296</v>
       </c>
       <c r="F16" s="3">
-        <v>7</v>
-      </c>
-      <c r="G16" s="10">
+        <v>9</v>
+      </c>
+      <c r="G16" s="16">
         <f t="shared" si="0"/>
-        <v>46280</v>
+        <v>46305</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D17" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="1"/>
-        <v>46281</v>
+        <v>46306</v>
       </c>
       <c r="F17" s="3">
-        <v>5</v>
-      </c>
-      <c r="G17" s="10">
+        <v>7</v>
+      </c>
+      <c r="G17" s="16">
         <f t="shared" si="0"/>
-        <v>46286</v>
+        <v>46313</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D18" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="1"/>
-        <v>46287</v>
+        <v>46314</v>
       </c>
       <c r="F18" s="3">
-        <v>15</v>
-      </c>
-      <c r="G18" s="10">
+        <v>19</v>
+      </c>
+      <c r="G18" s="16">
         <f t="shared" si="0"/>
-        <v>46302</v>
+        <v>46333</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="1"/>
-        <v>46303</v>
+        <v>46334</v>
       </c>
       <c r="F19" s="3">
-        <v>7</v>
-      </c>
-      <c r="G19" s="10">
+        <v>9</v>
+      </c>
+      <c r="G19" s="16">
         <f t="shared" si="0"/>
-        <v>46310</v>
+        <v>46343</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>64</v>
+        <v>50</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D20" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="9">
         <f>G19+1</f>
-        <v>46311</v>
+        <v>46344</v>
       </c>
       <c r="F20" s="3">
-        <v>7</v>
-      </c>
-      <c r="G20" s="10">
+        <v>9</v>
+      </c>
+      <c r="G20" s="16">
         <f t="shared" si="0"/>
-        <v>46318</v>
+        <v>46353</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="9">
         <f>G20+1</f>
-        <v>46319</v>
+        <v>46354</v>
       </c>
       <c r="F21" s="3">
-        <v>7</v>
-      </c>
-      <c r="G21" s="10">
+        <v>9</v>
+      </c>
+      <c r="G21" s="16">
         <f t="shared" si="0"/>
-        <v>46326</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46363</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15">
       <c r="C23" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="D23" s="12">
+        <f>G21</f>
+        <v>46363</v>
       </c>
     </row>
   </sheetData>
@@ -1413,13 +1506,13 @@
     <mergeCell ref="B1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H21">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>$P$5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>$P$3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>$P$4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1430,9 +1523,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1443,7 +1536,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
@@ -1458,35 +1551,35 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1495,15 +1588,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1512,15 +1605,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1529,15 +1622,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1546,15 +1639,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1563,15 +1656,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1580,15 +1673,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="399" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8317B7A6-5347-40B4-8672-8C5CE52D8653}"/>
+  <xr:revisionPtr revIDLastSave="400" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25B65384-2C40-4578-ADFB-AC7F8B49A189}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -261,7 +261,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,9 +379,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -393,6 +390,9 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,137 +705,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
   <dimension ref="A1:A34"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>46174</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>46175</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>46176</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>46177</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>46178</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>46179</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>46180</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>46181</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>46182</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>46183</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>46184</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>46185</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="6"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="6"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="6"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="6"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="6"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="6"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="6"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="6"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="6"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="6"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="6"/>
     </row>
   </sheetData>
@@ -846,28 +846,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:16" ht="30.75">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -886,17 +886,17 @@
       <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -913,14 +913,14 @@
       <c r="F3" s="3">
         <v>9</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="15">
         <f>E3+F3</f>
         <v>46190</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>14</v>
       </c>
       <c r="J3" s="2"/>
@@ -928,7 +928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -948,21 +948,21 @@
       <c r="F4" s="3">
         <v>18</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="15">
         <f t="shared" ref="G4:G21" si="0">E4+F4</f>
         <v>46209</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="P4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -982,21 +982,21 @@
       <c r="F5" s="3">
         <v>7</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="13" t="s">
         <v>14</v>
       </c>
       <c r="P5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1016,18 +1016,18 @@
       <c r="F6" s="3">
         <v>2</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <f t="shared" si="0"/>
         <v>46220</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="I6" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1047,18 +1047,18 @@
       <c r="F7" s="3">
         <v>7</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <f t="shared" si="0"/>
         <v>46228</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="I7" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1078,18 +1078,18 @@
       <c r="F8" s="3">
         <v>7</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <f t="shared" si="0"/>
         <v>46236</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>17</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1109,18 +1109,18 @@
       <c r="F9" s="3">
         <v>7</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <f t="shared" si="0"/>
         <v>46244</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="I9" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1140,18 +1140,18 @@
       <c r="F10" s="3">
         <v>10</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f t="shared" si="0"/>
         <v>46255</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="I10" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1171,18 +1171,18 @@
       <c r="F11" s="3">
         <v>7</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <f t="shared" si="0"/>
         <v>46263</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="I11" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1202,18 +1202,18 @@
       <c r="F12" s="3">
         <v>9</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <f t="shared" si="0"/>
         <v>46273</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="I12" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1233,18 +1233,18 @@
       <c r="F13" s="3">
         <v>9</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="I13" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1264,18 +1264,18 @@
       <c r="F14" s="3">
         <v>5</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="I14" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1295,18 +1295,18 @@
       <c r="F15" s="3">
         <v>5</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="15">
         <f t="shared" si="0"/>
         <v>46295</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="I15" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1326,18 +1326,18 @@
       <c r="F16" s="3">
         <v>9</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="15">
         <f t="shared" si="0"/>
         <v>46305</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="I16" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1357,18 +1357,18 @@
       <c r="F17" s="3">
         <v>7</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="15">
         <f t="shared" si="0"/>
         <v>46313</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="I17" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1388,18 +1388,18 @@
       <c r="F18" s="3">
         <v>19</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="15">
         <f t="shared" si="0"/>
         <v>46333</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="I18" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1419,18 +1419,18 @@
       <c r="F19" s="3">
         <v>9</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="15">
         <f t="shared" si="0"/>
         <v>46343</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I19" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="I19" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1450,18 +1450,18 @@
       <c r="F20" s="3">
         <v>9</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="15">
         <f t="shared" si="0"/>
         <v>46353</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="I20" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1481,22 +1481,22 @@
       <c r="F21" s="3">
         <v>9</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <f t="shared" si="0"/>
         <v>46363</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15">
+      <c r="I21" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>G21</f>
         <v>46363</v>
       </c>
@@ -1523,9 +1523,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25B65384-2C40-4578-ADFB-AC7F8B49A189}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2723F782-9EC4-4ADB-AC9A-E81367D9DF06}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>Database Design &amp; Architecture Setup</t>
-  </si>
-  <si>
-    <t>In-progress</t>
   </si>
   <si>
     <t>Not Started</t>
@@ -936,7 +933,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -946,20 +943,20 @@
         <v>46191</v>
       </c>
       <c r="F4" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G4" s="15">
         <f t="shared" ref="G4:G21" si="0">E4+F4</f>
-        <v>46209</v>
+        <v>46198</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="P4" t="s">
         <v>17</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -967,33 +964,33 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
       </c>
       <c r="E5" s="9">
         <f>G4+1</f>
-        <v>46210</v>
+        <v>46199</v>
       </c>
       <c r="F5" s="3">
         <v>7</v>
       </c>
       <c r="G5" s="15">
         <f t="shared" si="0"/>
-        <v>46217</v>
+        <v>46206</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>14</v>
       </c>
       <c r="P5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -1001,27 +998,27 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" ref="E6:E19" si="1">G5+1</f>
-        <v>46218</v>
+        <v>46207</v>
       </c>
       <c r="F6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>46220</v>
+        <v>46211</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>14</v>
@@ -1032,24 +1029,24 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="1"/>
-        <v>46221</v>
+        <v>46212</v>
       </c>
       <c r="F7" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G7" s="15">
         <f t="shared" si="0"/>
-        <v>46228</v>
+        <v>46216</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>13</v>
@@ -1063,24 +1060,24 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="1"/>
-        <v>46229</v>
+        <v>46217</v>
       </c>
       <c r="F8" s="3">
         <v>7</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>46236</v>
+        <v>46224</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>17</v>
@@ -1094,27 +1091,27 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="3">
         <v>6</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="1"/>
-        <v>46237</v>
+        <v>46225</v>
       </c>
       <c r="F9" s="3">
         <v>7</v>
       </c>
       <c r="G9" s="15">
         <f t="shared" si="0"/>
-        <v>46244</v>
+        <v>46232</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>14</v>
@@ -1125,27 +1122,27 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3">
         <v>7</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="1"/>
-        <v>46245</v>
+        <v>46233</v>
       </c>
       <c r="F10" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>46255</v>
+        <v>46240</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>14</v>
@@ -1156,27 +1153,27 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" si="1"/>
-        <v>46256</v>
+        <v>46241</v>
       </c>
       <c r="F11" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" s="15">
         <f t="shared" si="0"/>
-        <v>46263</v>
+        <v>46251</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>14</v>
@@ -1187,27 +1184,27 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3">
         <v>9</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" si="1"/>
-        <v>46264</v>
+        <v>46252</v>
       </c>
       <c r="F12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>46273</v>
+        <v>46259</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>14</v>
@@ -1218,27 +1215,27 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="3">
         <v>10</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="1"/>
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="F13" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="15">
         <f t="shared" si="0"/>
-        <v>46283</v>
+        <v>46267</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>14</v>
@@ -1249,27 +1246,27 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
         <v>11</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="1"/>
-        <v>46284</v>
+        <v>46268</v>
       </c>
       <c r="F14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>46289</v>
+        <v>46272</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>14</v>
@@ -1280,27 +1277,27 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3">
         <v>12</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="1"/>
-        <v>46290</v>
+        <v>46273</v>
       </c>
       <c r="F15" s="3">
         <v>5</v>
       </c>
       <c r="G15" s="15">
         <f t="shared" si="0"/>
-        <v>46295</v>
+        <v>46278</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>14</v>
@@ -1311,27 +1308,27 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="1"/>
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="F16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>46305</v>
+        <v>46287</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>14</v>
@@ -1342,27 +1339,27 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
       </c>
       <c r="E17" s="9">
         <f t="shared" si="1"/>
-        <v>46306</v>
+        <v>46288</v>
       </c>
       <c r="F17" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
         <f t="shared" si="0"/>
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>14</v>
@@ -1373,27 +1370,27 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
       </c>
       <c r="E18" s="9">
         <f t="shared" si="1"/>
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="F18" s="3">
         <v>19</v>
       </c>
       <c r="G18" s="15">
         <f t="shared" si="0"/>
-        <v>46333</v>
+        <v>46326</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>14</v>
@@ -1404,27 +1401,27 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="1"/>
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="F19" s="3">
         <v>9</v>
       </c>
       <c r="G19" s="15">
         <f t="shared" si="0"/>
-        <v>46343</v>
+        <v>46336</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>14</v>
@@ -1435,27 +1432,27 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
       </c>
       <c r="E20" s="9">
         <f>G19+1</f>
-        <v>46344</v>
+        <v>46337</v>
       </c>
       <c r="F20" s="3">
         <v>9</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>46353</v>
+        <v>46346</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>14</v>
@@ -1466,27 +1463,27 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
       </c>
       <c r="E21" s="9">
         <f>G20+1</f>
-        <v>46354</v>
+        <v>46347</v>
       </c>
       <c r="F21" s="3">
         <v>9</v>
       </c>
       <c r="G21" s="15">
         <f t="shared" si="0"/>
-        <v>46363</v>
+        <v>46356</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>14</v>
@@ -1494,11 +1491,11 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="11">
         <f>G21</f>
-        <v>46363</v>
+        <v>46356</v>
       </c>
     </row>
   </sheetData>
@@ -1536,7 +1533,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
@@ -1556,19 +1553,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>58</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1576,10 +1573,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1593,10 +1590,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1610,10 +1607,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>63</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1627,10 +1624,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1644,10 +1641,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
         <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1661,10 +1658,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
         <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1678,10 +1675,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
         <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30219"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2723F782-9EC4-4ADB-AC9A-E81367D9DF06}"/>
+  <xr:revisionPtr revIDLastSave="492" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC48B3EA-9294-42A7-91D6-A116C54D00DA}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,11 +38,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
   <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>WeekOff</t>
+  </si>
+  <si>
     <t>Tradesphere Project Tracker</t>
   </si>
   <si>
@@ -88,97 +94,100 @@
     <t>Phase 2</t>
   </si>
   <si>
+    <t>Authentication Module</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Phase 3</t>
+  </si>
+  <si>
+    <t>Security Module</t>
+  </si>
+  <si>
+    <t>In-Progress</t>
+  </si>
+  <si>
+    <t>Phase 4</t>
+  </si>
+  <si>
+    <t>Employee Module</t>
+  </si>
+  <si>
+    <t>Phase 5</t>
+  </si>
+  <si>
+    <t>Territory Module</t>
+  </si>
+  <si>
+    <t>Phase 6</t>
+  </si>
+  <si>
+    <t>Promoter Module</t>
+  </si>
+  <si>
+    <t>Phase 7</t>
+  </si>
+  <si>
+    <t>Beats &amp; Beat Assignment Module</t>
+  </si>
+  <si>
+    <t>Phase 8</t>
+  </si>
+  <si>
+    <t>Retailer Module</t>
+  </si>
+  <si>
+    <t>Phase 9</t>
+  </si>
+  <si>
+    <t>Attendance And EOD Module</t>
+  </si>
+  <si>
+    <t>Phase 10</t>
+  </si>
+  <si>
+    <t>Visit Module</t>
+  </si>
+  <si>
+    <t>Phase 11</t>
+  </si>
+  <si>
+    <t>Retailer Feedback Module</t>
+  </si>
+  <si>
+    <t>Phase 12</t>
+  </si>
+  <si>
+    <t>Product Module</t>
+  </si>
+  <si>
+    <t>Phase 13</t>
+  </si>
+  <si>
+    <t>Retailer Stock Management</t>
+  </si>
+  <si>
+    <t>Phase 14</t>
+  </si>
+  <si>
+    <t>Order Module</t>
+  </si>
+  <si>
+    <t>Phase 15</t>
+  </si>
+  <si>
     <t>Database Design &amp; Architecture Setup</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Phase 3</t>
-  </si>
-  <si>
-    <t>Authentication Module</t>
-  </si>
-  <si>
-    <t>In-Progress</t>
-  </si>
-  <si>
-    <t>Phase 4</t>
-  </si>
-  <si>
-    <t>Security Module</t>
-  </si>
-  <si>
-    <t>Phase 5</t>
-  </si>
-  <si>
-    <t>Employee Module</t>
-  </si>
-  <si>
-    <t>Phase 6</t>
-  </si>
-  <si>
-    <t>Territory Module</t>
-  </si>
-  <si>
-    <t>Phase 7</t>
-  </si>
-  <si>
-    <t>Promoter Module</t>
-  </si>
-  <si>
-    <t>Phase 8</t>
-  </si>
-  <si>
-    <t>Beats &amp; Beat Assignment Module</t>
-  </si>
-  <si>
-    <t>Phase 9</t>
-  </si>
-  <si>
-    <t>Retailer Module</t>
-  </si>
-  <si>
-    <t>Phase 10</t>
-  </si>
-  <si>
-    <t>Attendance And EOD Module</t>
-  </si>
-  <si>
-    <t>Phase 11</t>
-  </si>
-  <si>
-    <t>Visit Module</t>
-  </si>
-  <si>
-    <t>Phase 12</t>
-  </si>
-  <si>
-    <t>Retailer Feedback Module</t>
-  </si>
-  <si>
-    <t>Phase 13</t>
-  </si>
-  <si>
-    <t>Product Module</t>
-  </si>
-  <si>
-    <t>Phase 14</t>
-  </si>
-  <si>
-    <t>Retailer Stock Management</t>
-  </si>
-  <si>
-    <t>Phase 15</t>
-  </si>
-  <si>
-    <t>Order Module</t>
-  </si>
-  <si>
     <t>Phase 16</t>
   </si>
   <si>
     <t>UI/UX Design(Portal + App)</t>
+  </si>
+  <si>
+    <t>Planned to start in 3rd Week of July</t>
   </si>
   <si>
     <t>Phase 17</t>
@@ -258,7 +267,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,7 +376,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -390,6 +398,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -701,139 +710,356 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
-  <dimension ref="A1:A34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
+    <row r="2" spans="1:2">
+      <c r="A2" s="16">
         <v>46174</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="16">
         <v>46175</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="16">
         <v>46176</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="16">
         <v>46177</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="16">
         <v>46178</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="16">
         <v>46179</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="16">
         <v>46180</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="16">
         <v>46181</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="16">
         <v>46182</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="16">
         <v>46183</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="16">
         <v>46184</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="16">
         <v>46185</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A32" s="6"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6"/>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="16">
+        <v>46186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="16">
+        <v>46187</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="16">
+        <v>46188</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="16">
+        <v>46189</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="16">
+        <v>46191</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="16">
+        <v>46192</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16">
+        <v>46193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="16">
+        <v>46194</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="16">
+        <v>46195</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="16">
+        <v>46196</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="16">
+        <v>46197</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="16">
+        <v>46198</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="16">
+        <v>46199</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16">
+        <v>46200</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="16">
+        <v>46201</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="16">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="16">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="16">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="16">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="16">
+        <v>46207</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="16">
+        <v>46208</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="16">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="16">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="16">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="16">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="16">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="16">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="16">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="16">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="16">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="16">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="16">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="16">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="16">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="16">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="16">
+        <v>46223</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -843,162 +1069,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-    </row>
-    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="1" spans="1:16">
+      <c r="B1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+    </row>
+    <row r="2" spans="1:16" ht="29.1">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="H2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>46181</v>
       </c>
       <c r="F3" s="3">
         <v>9</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="14">
         <f>E3+F3</f>
         <v>46190</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="J3" s="2"/>
       <c r="P3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <f>G3+1</f>
         <v>46191</v>
       </c>
       <c r="F4" s="3">
         <v>7</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="14">
         <f t="shared" ref="G4:G21" si="0">E4+F4</f>
         <v>46198</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="P4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <f>G4+1</f>
         <v>46199</v>
       </c>
       <c r="F5" s="3">
         <v>7</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="14">
         <f t="shared" si="0"/>
         <v>46206</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="P5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>24</v>
@@ -1006,30 +1232,30 @@
       <c r="D6" s="3">
         <v>3</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <f t="shared" ref="E6:E19" si="1">G5+1</f>
         <v>46207</v>
       </c>
       <c r="F6" s="3">
         <v>4</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <f t="shared" si="0"/>
         <v>46211</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>26</v>
@@ -1037,30 +1263,30 @@
       <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <f t="shared" si="1"/>
         <v>46212</v>
       </c>
       <c r="F7" s="3">
         <v>4</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <f t="shared" si="0"/>
         <v>46216</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>28</v>
@@ -1068,30 +1294,30 @@
       <c r="D8" s="3">
         <v>5</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <f t="shared" si="1"/>
         <v>46217</v>
       </c>
       <c r="F8" s="3">
         <v>7</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <f t="shared" si="0"/>
         <v>46224</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>30</v>
@@ -1099,30 +1325,30 @@
       <c r="D9" s="3">
         <v>6</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <f t="shared" si="1"/>
         <v>46225</v>
       </c>
       <c r="F9" s="3">
         <v>7</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <f t="shared" si="0"/>
         <v>46232</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>32</v>
@@ -1130,30 +1356,30 @@
       <c r="D10" s="3">
         <v>7</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <f t="shared" si="1"/>
         <v>46233</v>
       </c>
       <c r="F10" s="3">
         <v>7</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <f t="shared" si="0"/>
         <v>46240</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>34</v>
@@ -1161,30 +1387,30 @@
       <c r="D11" s="3">
         <v>8</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <f t="shared" si="1"/>
         <v>46241</v>
       </c>
       <c r="F11" s="3">
         <v>10</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <f t="shared" si="0"/>
         <v>46251</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -1192,30 +1418,30 @@
       <c r="D12" s="3">
         <v>9</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <f t="shared" si="1"/>
         <v>46252</v>
       </c>
       <c r="F12" s="3">
         <v>7</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <f t="shared" si="0"/>
         <v>46259</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>38</v>
@@ -1223,30 +1449,30 @@
       <c r="D13" s="3">
         <v>10</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="8">
         <f t="shared" si="1"/>
         <v>46260</v>
       </c>
       <c r="F13" s="3">
         <v>7</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <f t="shared" si="0"/>
         <v>46267</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>40</v>
@@ -1254,30 +1480,30 @@
       <c r="D14" s="3">
         <v>11</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="8">
         <f t="shared" si="1"/>
         <v>46268</v>
       </c>
       <c r="F14" s="3">
         <v>4</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f t="shared" si="0"/>
         <v>46272</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>42</v>
@@ -1285,30 +1511,30 @@
       <c r="D15" s="3">
         <v>12</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <f t="shared" si="1"/>
         <v>46273</v>
       </c>
       <c r="F15" s="3">
         <v>5</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>44</v>
@@ -1316,184 +1542,187 @@
       <c r="D16" s="3">
         <v>13</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <f t="shared" si="1"/>
         <v>46279</v>
       </c>
       <c r="F16" s="3">
         <v>8</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <f t="shared" si="0"/>
         <v>46287</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <f t="shared" si="1"/>
         <v>46288</v>
       </c>
       <c r="F17" s="3">
         <v>18</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <f t="shared" si="0"/>
         <v>46306</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <f t="shared" si="1"/>
         <v>46307</v>
       </c>
       <c r="F18" s="3">
         <v>19</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <f t="shared" si="0"/>
         <v>46326</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <f t="shared" si="1"/>
         <v>46327</v>
       </c>
       <c r="F19" s="3">
         <v>9</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="14">
         <f t="shared" si="0"/>
         <v>46336</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <f>G19+1</f>
         <v>46337</v>
       </c>
       <c r="F20" s="3">
         <v>9</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <f t="shared" si="0"/>
         <v>46346</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <f>G20+1</f>
         <v>46347</v>
       </c>
       <c r="F21" s="3">
         <v>9</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="14">
         <f t="shared" si="0"/>
         <v>46356</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="11">
+        <v>56</v>
+      </c>
+      <c r="D23" s="10">
         <f>G21</f>
         <v>46356</v>
       </c>
@@ -1520,63 +1749,63 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1585,15 +1814,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1602,15 +1831,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1619,15 +1848,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1636,15 +1865,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1653,15 +1882,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -1670,15 +1899,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC48B3EA-9294-42A7-91D6-A116C54D00DA}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8EED81F-56EE-4182-8445-F9C94655C3C6}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -395,10 +395,10 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,256 +722,262 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="16">
+      <c r="A2" s="8">
         <v>46174</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="16">
+      <c r="A3" s="8">
         <v>46175</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="16">
+      <c r="A4" s="8">
         <v>46176</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="16">
+      <c r="A5" s="8">
         <v>46177</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="16">
+      <c r="A6" s="8">
         <v>46178</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="16">
+      <c r="A7" s="8">
         <v>46179</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="16">
+      <c r="A8" s="8">
         <v>46180</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="16">
+      <c r="A9" s="8">
         <v>46181</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="16">
+      <c r="A10" s="8">
         <v>46182</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="16">
+      <c r="A11" s="8">
         <v>46183</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="16">
+      <c r="A12" s="8">
         <v>46184</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="16">
+      <c r="A13" s="8">
         <v>46185</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="16">
+      <c r="A14" s="8">
         <v>46186</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="16">
+      <c r="A15" s="8">
         <v>46187</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="16">
+      <c r="A16" s="8">
         <v>46188</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="16">
+      <c r="A17" s="8">
         <v>46189</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="16">
+      <c r="A18" s="8">
         <v>46190</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="16">
+      <c r="A19" s="8">
         <v>46191</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="16">
+      <c r="A20" s="8">
         <v>46192</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="16">
+      <c r="A21" s="8">
         <v>46193</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="16">
+      <c r="A22" s="8">
         <v>46194</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="16">
+      <c r="A23" s="8">
         <v>46195</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="16">
+      <c r="A24" s="8">
         <v>46196</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="16">
+      <c r="A25" s="8">
         <v>46197</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="16">
+      <c r="A26" s="8">
         <v>46198</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="16">
+      <c r="A27" s="8">
         <v>46199</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="16">
+      <c r="A28" s="8">
         <v>46200</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="16">
+      <c r="A29" s="8">
         <v>46201</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="16">
+      <c r="A30" s="8">
         <v>46202</v>
       </c>
+      <c r="B30" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="16">
+      <c r="A31" s="8">
         <v>46203</v>
       </c>
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="16">
+      <c r="A32" s="15">
         <v>46204</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="16">
+      <c r="A33" s="15">
         <v>46205</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="16">
+      <c r="A34" s="15">
         <v>46206</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="16">
+      <c r="A35" s="15">
         <v>46207</v>
       </c>
       <c r="B35" t="s">
@@ -979,7 +985,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="16">
+      <c r="A36" s="15">
         <v>46208</v>
       </c>
       <c r="B36" t="s">
@@ -987,77 +993,77 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="16">
+      <c r="A37" s="15">
         <v>46209</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="16">
+      <c r="A38" s="15">
         <v>46210</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="16">
+      <c r="A39" s="15">
         <v>46211</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="16">
+      <c r="A40" s="15">
         <v>46212</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="16">
+      <c r="A41" s="15">
         <v>46213</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="16">
+      <c r="A42" s="15">
         <v>46214</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="16">
+      <c r="A43" s="15">
         <v>46215</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="16">
+      <c r="A44" s="15">
         <v>46216</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="16">
+      <c r="A45" s="15">
         <v>46217</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="16">
+      <c r="A46" s="15">
         <v>46218</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="16">
+      <c r="A47" s="15">
         <v>46219</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="16">
+      <c r="A48" s="15">
         <v>46220</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="16">
+      <c r="A49" s="15">
         <v>46221</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="16">
+      <c r="A50" s="15">
         <v>46222</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="16">
+      <c r="A51" s="15">
         <v>46223</v>
       </c>
     </row>
@@ -1082,13 +1088,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:16" ht="29.1">
       <c r="A2" s="6" t="s">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="495" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8EED81F-56EE-4182-8445-F9C94655C3C6}"/>
+  <xr:revisionPtr revIDLastSave="502" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010B6A38-FA3C-4324-8D6B-F0E5EE56594A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -367,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -395,15 +395,16 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -431,6 +432,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -710,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -954,120 +975,208 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="8">
+      <c r="A31" s="16">
         <v>46203</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="15">
+      <c r="A32" s="8">
         <v>46204</v>
       </c>
+      <c r="B32" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="15">
+      <c r="A33" s="8">
         <v>46205</v>
       </c>
+      <c r="B33" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="15">
+      <c r="A34" s="8">
         <v>46206</v>
       </c>
+      <c r="B34" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="15">
+      <c r="A35" s="8">
         <v>46207</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="15">
+      <c r="A36" s="8">
         <v>46208</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="15">
+      <c r="A37" s="8">
         <v>46209</v>
       </c>
+      <c r="B37" s="3"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="15">
+      <c r="A38" s="8">
         <v>46210</v>
       </c>
+      <c r="B38" s="3"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="15">
+      <c r="A39" s="8">
         <v>46211</v>
       </c>
+      <c r="B39" s="3"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="15">
+      <c r="A40" s="8">
         <v>46212</v>
       </c>
+      <c r="B40" s="3"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="15">
+      <c r="A41" s="8">
         <v>46213</v>
       </c>
+      <c r="B41" s="3"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="15">
+      <c r="A42" s="8">
         <v>46214</v>
       </c>
+      <c r="B42" s="3"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="15">
+      <c r="A43" s="8">
         <v>46215</v>
       </c>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="15">
+      <c r="A44" s="8">
         <v>46216</v>
       </c>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="15">
+      <c r="A45" s="8">
         <v>46217</v>
       </c>
+      <c r="B45" s="3"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="15">
+      <c r="A46" s="8">
         <v>46218</v>
       </c>
+      <c r="B46" s="3"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="15">
+      <c r="A47" s="8">
         <v>46219</v>
       </c>
+      <c r="B47" s="3"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="15">
+      <c r="A48" s="8">
         <v>46220</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="15">
+      <c r="B48" s="3"/>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="8">
         <v>46221</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="15">
+      <c r="B49" s="3"/>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="8">
         <v>46222</v>
       </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="15">
+      <c r="B50" s="3"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="8">
         <v>46223</v>
       </c>
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="8">
+        <v>46224</v>
+      </c>
+      <c r="B52" s="3"/>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="8">
+        <v>46225</v>
+      </c>
+      <c r="B53" s="3"/>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="8">
+        <v>46226</v>
+      </c>
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="8">
+        <v>46227</v>
+      </c>
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="8">
+        <v>46228</v>
+      </c>
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="8">
+        <v>46229</v>
+      </c>
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="8">
+        <v>46230</v>
+      </c>
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="8">
+        <v>46231</v>
+      </c>
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="8">
+        <v>46232</v>
+      </c>
+      <c r="B60" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+      <formula>"Present"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"WeekOff"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1088,13 +1197,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:16" ht="29.1">
       <c r="A2" s="6" t="s">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="502" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010B6A38-FA3C-4324-8D6B-F0E5EE56594A}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BAE026-BEC1-414A-904B-7D15A3B575C5}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -267,7 +267,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,11 +395,11 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,21 +437,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -732,17 +732,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>46174</v>
       </c>
@@ -750,7 +750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>46175</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>46176</v>
       </c>
@@ -766,7 +766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>46177</v>
       </c>
@@ -774,7 +774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>46178</v>
       </c>
@@ -782,7 +782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>46179</v>
       </c>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>46180</v>
       </c>
@@ -798,7 +798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>46181</v>
       </c>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>46182</v>
       </c>
@@ -814,7 +814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>46183</v>
       </c>
@@ -822,7 +822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>46184</v>
       </c>
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>46185</v>
       </c>
@@ -838,7 +838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>46186</v>
       </c>
@@ -846,7 +846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>46187</v>
       </c>
@@ -854,7 +854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>46188</v>
       </c>
@@ -862,7 +862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>46189</v>
       </c>
@@ -870,7 +870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>46190</v>
       </c>
@@ -878,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>46191</v>
       </c>
@@ -886,7 +886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>46192</v>
       </c>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>46193</v>
       </c>
@@ -902,7 +902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>46194</v>
       </c>
@@ -910,7 +910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>46195</v>
       </c>
@@ -918,7 +918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>46196</v>
       </c>
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>46197</v>
       </c>
@@ -934,7 +934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>46198</v>
       </c>
@@ -942,7 +942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>46199</v>
       </c>
@@ -950,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>46200</v>
       </c>
@@ -958,7 +958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>46201</v>
       </c>
@@ -966,7 +966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>46202</v>
       </c>
@@ -974,15 +974,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="16">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="15">
         <v>46203</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+      <c r="B31" s="16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>46204</v>
       </c>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>46205</v>
       </c>
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>46206</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>46207</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>46208</v>
       </c>
@@ -1022,145 +1022,145 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
       <c r="B37" s="3"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>46210</v>
       </c>
       <c r="B38" s="3"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>46211</v>
       </c>
       <c r="B39" s="3"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>46212</v>
       </c>
       <c r="B40" s="3"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>46213</v>
       </c>
       <c r="B41" s="3"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>46214</v>
       </c>
       <c r="B42" s="3"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>46215</v>
       </c>
       <c r="B43" s="3"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>46216</v>
       </c>
       <c r="B44" s="3"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>46217</v>
       </c>
       <c r="B45" s="3"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>46218</v>
       </c>
       <c r="B46" s="3"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>46219</v>
       </c>
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>46220</v>
       </c>
       <c r="B48" s="3"/>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>46221</v>
       </c>
       <c r="B49" s="3"/>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>46222</v>
       </c>
       <c r="B50" s="3"/>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>46223</v>
       </c>
       <c r="B51" s="3"/>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>46224</v>
       </c>
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>46225</v>
       </c>
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>46226</v>
       </c>
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>46227</v>
       </c>
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>46228</v>
       </c>
       <c r="B56" s="3"/>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>46229</v>
       </c>
       <c r="B57" s="3"/>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>46230</v>
       </c>
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>46231</v>
       </c>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>46232</v>
       </c>
@@ -1168,13 +1168,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"WeekOff"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Present"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"WeekOff"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1184,28 +1182,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="2" spans="1:16" ht="29.1">
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -1234,7 +1232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1266,7 +1264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1300,7 +1298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1325,7 +1323,7 @@
         <v>46206</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>16</v>
@@ -1334,7 +1332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1365,7 +1363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1396,7 +1394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1414,20 +1412,20 @@
         <v>46217</v>
       </c>
       <c r="F8" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" s="14">
         <f t="shared" si="0"/>
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1442,14 +1440,14 @@
       </c>
       <c r="E9" s="8">
         <f t="shared" si="1"/>
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="F9" s="3">
         <v>7</v>
       </c>
       <c r="G9" s="14">
         <f t="shared" si="0"/>
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>19</v>
@@ -1458,7 +1456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1473,23 +1471,23 @@
       </c>
       <c r="E10" s="8">
         <f t="shared" si="1"/>
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="F10" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10" s="14">
         <f t="shared" si="0"/>
-        <v>46240</v>
+        <v>46236</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1504,14 +1502,14 @@
       </c>
       <c r="E11" s="8">
         <f t="shared" si="1"/>
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="F11" s="3">
         <v>10</v>
       </c>
       <c r="G11" s="14">
         <f t="shared" si="0"/>
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>19</v>
@@ -1520,7 +1518,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1535,14 +1533,14 @@
       </c>
       <c r="E12" s="8">
         <f t="shared" si="1"/>
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="F12" s="3">
         <v>7</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" si="0"/>
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>19</v>
@@ -1551,7 +1549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1566,14 +1564,14 @@
       </c>
       <c r="E13" s="8">
         <f t="shared" si="1"/>
-        <v>46260</v>
+        <v>46256</v>
       </c>
       <c r="F13" s="3">
         <v>7</v>
       </c>
       <c r="G13" s="14">
         <f t="shared" si="0"/>
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>19</v>
@@ -1582,7 +1580,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1597,14 +1595,14 @@
       </c>
       <c r="E14" s="8">
         <f t="shared" si="1"/>
-        <v>46268</v>
+        <v>46264</v>
       </c>
       <c r="F14" s="3">
         <v>4</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="0"/>
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>19</v>
@@ -1613,7 +1611,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1628,14 +1626,14 @@
       </c>
       <c r="E15" s="8">
         <f t="shared" si="1"/>
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="F15" s="3">
         <v>5</v>
       </c>
       <c r="G15" s="14">
         <f t="shared" si="0"/>
-        <v>46278</v>
+        <v>46274</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>19</v>
@@ -1644,7 +1642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1659,14 +1657,14 @@
       </c>
       <c r="E16" s="8">
         <f t="shared" si="1"/>
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="F16" s="3">
         <v>8</v>
       </c>
       <c r="G16" s="14">
         <f t="shared" si="0"/>
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>19</v>
@@ -1675,7 +1673,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1690,14 +1688,14 @@
       </c>
       <c r="E17" s="8">
         <f t="shared" si="1"/>
-        <v>46288</v>
+        <v>46284</v>
       </c>
       <c r="F17" s="3">
         <v>18</v>
       </c>
       <c r="G17" s="14">
         <f t="shared" si="0"/>
-        <v>46306</v>
+        <v>46302</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>22</v>
@@ -1706,7 +1704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1721,14 +1719,14 @@
       </c>
       <c r="E18" s="8">
         <f t="shared" si="1"/>
-        <v>46307</v>
+        <v>46303</v>
       </c>
       <c r="F18" s="3">
         <v>19</v>
       </c>
       <c r="G18" s="14">
         <f t="shared" si="0"/>
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>19</v>
@@ -1740,7 +1738,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1755,14 +1753,14 @@
       </c>
       <c r="E19" s="8">
         <f t="shared" si="1"/>
-        <v>46327</v>
+        <v>46323</v>
       </c>
       <c r="F19" s="3">
         <v>9</v>
       </c>
       <c r="G19" s="14">
         <f t="shared" si="0"/>
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>19</v>
@@ -1771,7 +1769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1786,14 +1784,14 @@
       </c>
       <c r="E20" s="8">
         <f>G19+1</f>
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="F20" s="3">
         <v>9</v>
       </c>
       <c r="G20" s="14">
         <f t="shared" si="0"/>
-        <v>46346</v>
+        <v>46342</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>19</v>
@@ -1802,7 +1800,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1817,14 +1815,14 @@
       </c>
       <c r="E21" s="8">
         <f>G20+1</f>
-        <v>46347</v>
+        <v>46343</v>
       </c>
       <c r="F21" s="3">
         <v>9</v>
       </c>
       <c r="G21" s="14">
         <f t="shared" si="0"/>
-        <v>46356</v>
+        <v>46352</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>19</v>
@@ -1833,13 +1831,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D23" s="10">
         <f>G21</f>
-        <v>46356</v>
+        <v>46352</v>
       </c>
     </row>
   </sheetData>
@@ -1864,9 +1862,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -1892,7 +1890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1912,7 +1910,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1929,7 +1927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1946,7 +1944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1963,7 +1961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1980,7 +1978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1997,7 +1995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2014,7 +2012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76BAE026-BEC1-414A-904B-7D15A3B575C5}"/>
+  <xr:revisionPtr revIDLastSave="508" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB553083-A726-404D-B66F-044C0151ED47}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1026,7 +1026,9 @@
       <c r="A37" s="8">
         <v>46209</v>
       </c>
-      <c r="B37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="508" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB553083-A726-404D-B66F-044C0151ED47}"/>
+  <xr:revisionPtr revIDLastSave="509" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C447CF16-F258-41AB-ABC4-BA918A05DAA4}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1034,7 +1034,9 @@
       <c r="A38" s="8">
         <v>46210</v>
       </c>
-      <c r="B38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C447CF16-F258-41AB-ABC4-BA918A05DAA4}"/>
+  <xr:revisionPtr revIDLastSave="511" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50AC04F1-B4E1-47B9-8C0F-E46B050BDCF0}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -1454,7 +1454,7 @@
         <v>46230</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>16</v>
@@ -1485,7 +1485,7 @@
         <v>46236</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>16</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50AC04F1-B4E1-47B9-8C0F-E46B050BDCF0}"/>
+  <xr:revisionPtr revIDLastSave="512" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4D4028B-F75A-4BAB-87A2-90C65181DC1C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1042,7 +1042,9 @@
       <c r="A39" s="8">
         <v>46211</v>
       </c>
-      <c r="B39" s="3"/>
+      <c r="B39" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="512" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4D4028B-F75A-4BAB-87A2-90C65181DC1C}"/>
+  <xr:revisionPtr revIDLastSave="513" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B82C4A-3268-4283-A25D-655CC3EA2828}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1050,7 +1050,9 @@
       <c r="A40" s="8">
         <v>46212</v>
       </c>
-      <c r="B40" s="3"/>
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B82C4A-3268-4283-A25D-655CC3EA2828}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{480EE0AB-2328-4D42-88C2-D33718E53118}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1058,7 +1058,9 @@
       <c r="A41" s="8">
         <v>46213</v>
       </c>
-      <c r="B41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{480EE0AB-2328-4D42-88C2-D33718E53118}"/>
+  <xr:revisionPtr revIDLastSave="515" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5693EDD-D628-4B26-BC15-5CBB25E0C6B2}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Project Timeline" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -205,9 +206,6 @@
     <t>Phase 19</t>
   </si>
   <si>
-    <t>Deployment And Go-live Suppot</t>
-  </si>
-  <si>
     <t>Final Date</t>
   </si>
   <si>
@@ -257,6 +255,9 @@
   </si>
   <si>
     <t>Production Deployment</t>
+  </si>
+  <si>
+    <t>Deployment And Go-live Support</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1819,7 @@
         <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
@@ -1843,7 +1844,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="10">
         <f>G21</f>
@@ -1885,7 +1886,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>8</v>
@@ -1905,13 +1906,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>60</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -1925,10 +1926,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1942,10 +1943,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
         <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1959,10 +1960,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
         <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1976,10 +1977,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1993,10 +1994,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
         <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2010,10 +2011,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
         <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>70</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2027,10 +2028,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
         <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="515" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5693EDD-D628-4B26-BC15-5CBB25E0C6B2}"/>
+  <xr:revisionPtr revIDLastSave="518" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FD8536-4622-47D7-93E6-D9DD4D6A3A9C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Project Timeline" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1067,19 +1066,25 @@
       <c r="A42" s="8">
         <v>46214</v>
       </c>
-      <c r="B42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>46215</v>
       </c>
-      <c r="B43" s="3"/>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>46216</v>
       </c>
-      <c r="B44" s="3"/>
+      <c r="B44" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="518" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FD8536-4622-47D7-93E6-D9DD4D6A3A9C}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F2B57C-B293-4885-8A09-910330242552}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -267,7 +267,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,6 +287,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -367,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -400,6 +407,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1201,7 +1209,7 @@
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" customWidth="1"/>
     <col min="4" max="4" width="13.26953125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
@@ -1520,7 +1528,7 @@
         <f t="shared" si="1"/>
         <v>46237</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="18">
         <v>10</v>
       </c>
       <c r="G11" s="14">
@@ -1582,7 +1590,7 @@
         <f t="shared" si="1"/>
         <v>46256</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="18">
         <v>7</v>
       </c>
       <c r="G13" s="14">
@@ -1706,7 +1714,7 @@
         <f t="shared" si="1"/>
         <v>46284</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="18">
         <v>18</v>
       </c>
       <c r="G17" s="14">
@@ -1737,7 +1745,7 @@
         <f t="shared" si="1"/>
         <v>46303</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="18">
         <v>19</v>
       </c>
       <c r="G18" s="14">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="524" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F2B57C-B293-4885-8A09-910330242552}"/>
+  <xr:revisionPtr revIDLastSave="533" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A7E49DE-2591-463E-BBF6-D3BEBB4EBEE1}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="73">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -160,9 +160,6 @@
     <t>Phase 12</t>
   </si>
   <si>
-    <t>Product Module</t>
-  </si>
-  <si>
     <t>Phase 13</t>
   </si>
   <si>
@@ -257,6 +254,9 @@
   </si>
   <si>
     <t>Deployment And Go-live Support</t>
+  </si>
+  <si>
+    <t>Product module</t>
   </si>
 </sst>
 </file>
@@ -404,10 +404,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1098,7 +1098,9 @@
       <c r="A45" s="8">
         <v>46217</v>
       </c>
-      <c r="B45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
@@ -1219,13 +1221,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
@@ -1474,7 +1476,7 @@
         <v>46230</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>16</v>
@@ -1519,7 +1521,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
@@ -1528,15 +1530,15 @@
         <f t="shared" si="1"/>
         <v>46237</v>
       </c>
-      <c r="F11" s="18">
-        <v>10</v>
+      <c r="F11" s="17">
+        <v>4</v>
       </c>
       <c r="G11" s="14">
         <f t="shared" si="0"/>
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>16</v>
@@ -1557,14 +1559,14 @@
       </c>
       <c r="E12" s="8">
         <f t="shared" si="1"/>
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="F12" s="3">
         <v>7</v>
       </c>
       <c r="G12" s="14">
         <f t="shared" si="0"/>
-        <v>46255</v>
+        <v>46249</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>19</v>
@@ -1588,14 +1590,14 @@
       </c>
       <c r="E13" s="8">
         <f t="shared" si="1"/>
-        <v>46256</v>
-      </c>
-      <c r="F13" s="18">
+        <v>46250</v>
+      </c>
+      <c r="F13" s="17">
         <v>7</v>
       </c>
       <c r="G13" s="14">
         <f t="shared" si="0"/>
-        <v>46263</v>
+        <v>46257</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>19</v>
@@ -1612,17 +1614,17 @@
         <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3">
         <v>11</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" si="1"/>
-        <v>46264</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4</v>
+        <v>46258</v>
+      </c>
+      <c r="F14" s="17">
+        <v>10</v>
       </c>
       <c r="G14" s="14">
         <f t="shared" si="0"/>
@@ -1640,10 +1642,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="3">
         <v>12</v>
@@ -1671,10 +1673,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
@@ -1702,10 +1704,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
         <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
@@ -1714,7 +1716,7 @@
         <f t="shared" si="1"/>
         <v>46284</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>18</v>
       </c>
       <c r="G17" s="14">
@@ -1733,10 +1735,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
@@ -1745,7 +1747,7 @@
         <f t="shared" si="1"/>
         <v>46303</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <v>19</v>
       </c>
       <c r="G18" s="14">
@@ -1759,7 +1761,7 @@
         <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -1767,10 +1769,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
@@ -1798,10 +1800,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
@@ -1829,10 +1831,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
@@ -1857,7 +1859,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="10">
         <f>G21</f>
@@ -1899,7 +1901,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>8</v>
@@ -1919,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>59</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -1939,10 +1941,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1956,10 +1958,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
         <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1973,10 +1975,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -1990,10 +1992,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2007,10 +2009,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
         <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2024,10 +2026,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" t="s">
         <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2041,10 +2043,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="533" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A7E49DE-2591-463E-BBF6-D3BEBB4EBEE1}"/>
+  <xr:revisionPtr revIDLastSave="535" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FB5A7C2-81BD-479F-A55D-C29D4681D246}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="74">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Product module</t>
+  </si>
+  <si>
+    <t>halfday</t>
   </si>
 </sst>
 </file>
@@ -1106,13 +1109,17 @@
       <c r="A46" s="8">
         <v>46218</v>
       </c>
-      <c r="B46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>46219</v>
       </c>
-      <c r="B47" s="3"/>
+      <c r="B47" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="535" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FB5A7C2-81BD-479F-A55D-C29D4681D246}"/>
+  <xr:revisionPtr revIDLastSave="538" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23067961-E0DA-4537-ACB3-DD6202731D9A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="74">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1125,19 +1125,25 @@
       <c r="A48" s="8">
         <v>46220</v>
       </c>
-      <c r="B48" s="3"/>
+      <c r="B48" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>46221</v>
       </c>
-      <c r="B49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>46222</v>
       </c>
-      <c r="B50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30309"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="538" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23067961-E0DA-4537-ACB3-DD6202731D9A}"/>
+  <xr:revisionPtr revIDLastSave="543" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B5B534-AD42-44FF-A243-F930FA05171C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -49,6 +49,12 @@
     <t>WeekOff</t>
   </si>
   <si>
+    <t>halfday</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
     <t>Tradesphere Project Tracker</t>
   </si>
   <si>
@@ -142,24 +148,27 @@
     <t>Phase 9</t>
   </si>
   <si>
+    <t>Product module</t>
+  </si>
+  <si>
+    <t>Phase 10</t>
+  </si>
+  <si>
+    <t>Visit Module</t>
+  </si>
+  <si>
+    <t>Phase 11</t>
+  </si>
+  <si>
+    <t>Retailer Feedback Module</t>
+  </si>
+  <si>
+    <t>Phase 12</t>
+  </si>
+  <si>
     <t>Attendance And EOD Module</t>
   </si>
   <si>
-    <t>Phase 10</t>
-  </si>
-  <si>
-    <t>Visit Module</t>
-  </si>
-  <si>
-    <t>Phase 11</t>
-  </si>
-  <si>
-    <t>Retailer Feedback Module</t>
-  </si>
-  <si>
-    <t>Phase 12</t>
-  </si>
-  <si>
     <t>Phase 13</t>
   </si>
   <si>
@@ -202,6 +211,9 @@
     <t>Phase 19</t>
   </si>
   <si>
+    <t>Deployment And Go-live Support</t>
+  </si>
+  <si>
     <t>Final Date</t>
   </si>
   <si>
@@ -251,15 +263,6 @@
   </si>
   <si>
     <t>Production Deployment</t>
-  </si>
-  <si>
-    <t>Deployment And Go-live Support</t>
-  </si>
-  <si>
-    <t>Product module</t>
-  </si>
-  <si>
-    <t>halfday</t>
   </si>
 </sst>
 </file>
@@ -270,7 +273,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,17 +746,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" s="8">
         <v>46174</v>
       </c>
@@ -761,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" s="8">
         <v>46175</v>
       </c>
@@ -769,7 +772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" s="8">
         <v>46176</v>
       </c>
@@ -777,7 +780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" s="8">
         <v>46177</v>
       </c>
@@ -785,7 +788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" s="8">
         <v>46178</v>
       </c>
@@ -793,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" s="8">
         <v>46179</v>
       </c>
@@ -801,7 +804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" s="8">
         <v>46180</v>
       </c>
@@ -809,7 +812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" s="8">
         <v>46181</v>
       </c>
@@ -817,7 +820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" s="8">
         <v>46182</v>
       </c>
@@ -825,7 +828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" s="8">
         <v>46183</v>
       </c>
@@ -833,7 +836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" s="8">
         <v>46184</v>
       </c>
@@ -841,7 +844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" s="8">
         <v>46185</v>
       </c>
@@ -849,7 +852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" s="8">
         <v>46186</v>
       </c>
@@ -857,7 +860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2">
       <c r="A15" s="8">
         <v>46187</v>
       </c>
@@ -865,7 +868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2">
       <c r="A16" s="8">
         <v>46188</v>
       </c>
@@ -873,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" s="8">
         <v>46189</v>
       </c>
@@ -881,7 +884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2">
       <c r="A18" s="8">
         <v>46190</v>
       </c>
@@ -889,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2">
       <c r="A19" s="8">
         <v>46191</v>
       </c>
@@ -897,7 +900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2">
       <c r="A20" s="8">
         <v>46192</v>
       </c>
@@ -905,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2">
       <c r="A21" s="8">
         <v>46193</v>
       </c>
@@ -913,7 +916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2">
       <c r="A22" s="8">
         <v>46194</v>
       </c>
@@ -921,7 +924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2">
       <c r="A23" s="8">
         <v>46195</v>
       </c>
@@ -929,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2">
       <c r="A24" s="8">
         <v>46196</v>
       </c>
@@ -937,7 +940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2">
       <c r="A25" s="8">
         <v>46197</v>
       </c>
@@ -945,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2">
       <c r="A26" s="8">
         <v>46198</v>
       </c>
@@ -953,7 +956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2">
       <c r="A27" s="8">
         <v>46199</v>
       </c>
@@ -961,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2">
       <c r="A28" s="8">
         <v>46200</v>
       </c>
@@ -969,7 +972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2">
       <c r="A29" s="8">
         <v>46201</v>
       </c>
@@ -977,7 +980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2">
       <c r="A30" s="8">
         <v>46202</v>
       </c>
@@ -985,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2">
       <c r="A31" s="15">
         <v>46203</v>
       </c>
@@ -993,7 +996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2">
       <c r="A32" s="8">
         <v>46204</v>
       </c>
@@ -1001,7 +1004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2">
       <c r="A33" s="8">
         <v>46205</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2">
       <c r="A34" s="8">
         <v>46206</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2">
       <c r="A35" s="8">
         <v>46207</v>
       </c>
@@ -1025,7 +1028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2">
       <c r="A36" s="8">
         <v>46208</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
@@ -1041,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2">
       <c r="A38" s="8">
         <v>46210</v>
       </c>
@@ -1049,7 +1052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2">
       <c r="A39" s="8">
         <v>46211</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2">
       <c r="A40" s="8">
         <v>46212</v>
       </c>
@@ -1065,7 +1068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2">
       <c r="A41" s="8">
         <v>46213</v>
       </c>
@@ -1073,7 +1076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2">
       <c r="A42" s="8">
         <v>46214</v>
       </c>
@@ -1081,7 +1084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2">
       <c r="A43" s="8">
         <v>46215</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2">
       <c r="A44" s="8">
         <v>46216</v>
       </c>
@@ -1097,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2">
       <c r="A45" s="8">
         <v>46217</v>
       </c>
@@ -1105,15 +1108,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2">
       <c r="A46" s="8">
         <v>46218</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="8">
         <v>46219</v>
       </c>
@@ -1121,7 +1124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2">
       <c r="A48" s="8">
         <v>46220</v>
       </c>
@@ -1129,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2">
       <c r="A49" s="8">
         <v>46221</v>
       </c>
@@ -1137,7 +1140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2">
       <c r="A50" s="8">
         <v>46222</v>
       </c>
@@ -1145,61 +1148,69 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2">
       <c r="A51" s="8">
         <v>46223</v>
       </c>
-      <c r="B51" s="3"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="8">
         <v>46224</v>
       </c>
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2">
       <c r="A53" s="8">
         <v>46225</v>
       </c>
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2">
       <c r="A54" s="8">
         <v>46226</v>
       </c>
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2">
       <c r="A55" s="8">
         <v>46227</v>
       </c>
-      <c r="B55" s="3"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B55" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="8">
         <v>46228</v>
       </c>
-      <c r="B56" s="3"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="8">
         <v>46229</v>
       </c>
-      <c r="B57" s="3"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="8">
         <v>46230</v>
       </c>
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2">
       <c r="A59" s="8">
         <v>46231</v>
       </c>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2">
       <c r="A60" s="8">
         <v>46232</v>
       </c>
@@ -1221,65 +1232,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
       <c r="B1" s="18" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
     </row>
-    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="29.1">
       <c r="A2" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="8">
@@ -1293,25 +1304,25 @@
         <v>46190</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2"/>
       <c r="P3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1328,24 +1339,24 @@
         <v>46198</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -1362,24 +1373,24 @@
         <v>46206</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -1396,21 +1407,21 @@
         <v>46211</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
@@ -1427,21 +1438,21 @@
         <v>46216</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
@@ -1458,21 +1469,21 @@
         <v>46222</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3">
         <v>6</v>
@@ -1489,21 +1500,21 @@
         <v>46230</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="3">
         <v>7</v>
@@ -1520,21 +1531,21 @@
         <v>46236</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
@@ -1551,21 +1562,21 @@
         <v>46241</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3">
         <v>9</v>
@@ -1582,21 +1593,21 @@
         <v>46249</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" s="3">
         <v>10</v>
@@ -1613,21 +1624,21 @@
         <v>46257</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D14" s="3">
         <v>11</v>
@@ -1644,21 +1655,21 @@
         <v>46268</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D15" s="3">
         <v>12</v>
@@ -1675,21 +1686,21 @@
         <v>46274</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
@@ -1706,21 +1717,21 @@
         <v>46283</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
@@ -1737,21 +1748,21 @@
         <v>46302</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
@@ -1768,24 +1779,24 @@
         <v>46322</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
@@ -1802,21 +1813,21 @@
         <v>46332</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
@@ -1833,21 +1844,21 @@
         <v>46342</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
@@ -1864,15 +1875,15 @@
         <v>46352</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D23" s="10">
         <f>G21</f>
@@ -1901,63 +1912,63 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1966,15 +1977,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1983,15 +1994,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2000,15 +2011,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2017,15 +2028,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2034,15 +2045,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2051,15 +2062,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="543" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B5B534-AD42-44FF-A243-F930FA05171C}"/>
+  <xr:revisionPtr revIDLastSave="545" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C7FCA8B-8E18-4F05-8FF9-95B1F29BF057}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -273,7 +273,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,17 +746,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>46174</v>
       </c>
@@ -764,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>46175</v>
       </c>
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>46176</v>
       </c>
@@ -780,7 +780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>46177</v>
       </c>
@@ -788,7 +788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>46178</v>
       </c>
@@ -796,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>46179</v>
       </c>
@@ -804,7 +804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>46180</v>
       </c>
@@ -812,7 +812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>46181</v>
       </c>
@@ -820,7 +820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>46182</v>
       </c>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>46183</v>
       </c>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>46184</v>
       </c>
@@ -844,7 +844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>46185</v>
       </c>
@@ -852,7 +852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>46186</v>
       </c>
@@ -860,7 +860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>46187</v>
       </c>
@@ -868,7 +868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>46188</v>
       </c>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>46189</v>
       </c>
@@ -884,7 +884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>46190</v>
       </c>
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>46191</v>
       </c>
@@ -900,7 +900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>46192</v>
       </c>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>46193</v>
       </c>
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>46194</v>
       </c>
@@ -924,7 +924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>46195</v>
       </c>
@@ -932,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>46196</v>
       </c>
@@ -940,7 +940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>46197</v>
       </c>
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>46198</v>
       </c>
@@ -956,7 +956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>46199</v>
       </c>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>46200</v>
       </c>
@@ -972,7 +972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>46201</v>
       </c>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>46202</v>
       </c>
@@ -988,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="15">
         <v>46203</v>
       </c>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>46204</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>46205</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>46206</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>46207</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>46208</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>46210</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>46211</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>46212</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>46213</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>46214</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>46215</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>46216</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>46217</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>46218</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>46219</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>46220</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>46221</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>46222</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>46223</v>
       </c>
@@ -1156,33 +1156,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>46224</v>
       </c>
-      <c r="B52" s="3"/>
-    </row>
-    <row r="53" spans="1:2">
+      <c r="B52" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>46225</v>
       </c>
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>46226</v>
       </c>
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>46227</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>46228</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>46229</v>
       </c>
@@ -1198,19 +1198,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>46230</v>
       </c>
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>46231</v>
       </c>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>46232</v>
       </c>
@@ -1232,19 +1232,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
         <v>5</v>
       </c>
@@ -1253,7 +1253,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
     </row>
-    <row r="2" spans="1:16" ht="29.1">
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
         <v>58</v>
       </c>
@@ -1912,9 +1912,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="545" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C7FCA8B-8E18-4F05-8FF9-95B1F29BF057}"/>
+  <xr:revisionPtr revIDLastSave="548" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E727BAE-23EA-424A-8D0A-E24ACCCC24FE}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -480,6 +480,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1168,7 +1172,9 @@
       <c r="A53" s="8">
         <v>46225</v>
       </c>
-      <c r="B53" s="3"/>
+      <c r="B53" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
@@ -1562,7 +1568,7 @@
         <v>46241</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I11" s="12" t="s">
         <v>18</v>
@@ -1593,7 +1599,7 @@
         <v>46249</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>18</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="548" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E727BAE-23EA-424A-8D0A-E24ACCCC24FE}"/>
+  <xr:revisionPtr revIDLastSave="554" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5D4841-F0E1-4FF6-9404-F9365F96ED1B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -380,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -411,6 +411,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -480,10 +482,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -749,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -1180,13 +1178,17 @@
       <c r="A54" s="8">
         <v>46226</v>
       </c>
-      <c r="B54" s="3"/>
+      <c r="B54" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>46227</v>
       </c>
-      <c r="B55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
@@ -1221,6 +1223,16 @@
         <v>46232</v>
       </c>
       <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="18">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="19">
+        <v>46234</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
@@ -1251,13 +1263,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="554" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5D4841-F0E1-4FF6-9404-F9365F96ED1B}"/>
+  <xr:revisionPtr revIDLastSave="555" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E439D6E-C0D0-4C97-A58D-23172535CB0C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1210,7 +1210,9 @@
       <c r="A58" s="8">
         <v>46230</v>
       </c>
-      <c r="B58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="8">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="555" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E439D6E-C0D0-4C97-A58D-23172535CB0C}"/>
+  <xr:revisionPtr revIDLastSave="557" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F72199E-F5F5-4719-A545-E7FBF24AE585}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1218,13 +1218,17 @@
       <c r="A59" s="8">
         <v>46231</v>
       </c>
-      <c r="B59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>46232</v>
       </c>
-      <c r="B60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="18">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="557" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F72199E-F5F5-4719-A545-E7FBF24AE585}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9D76900-B06A-4BF3-B1F8-E812A5A853F1}"/>
   <bookViews>
     <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -380,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -416,6 +416,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1234,6 +1235,9 @@
       <c r="A61" s="18">
         <v>46233</v>
       </c>
+      <c r="B61" s="21" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="19">

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9D76900-B06A-4BF3-B1F8-E812A5A853F1}"/>
+  <xr:revisionPtr revIDLastSave="559" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65164B07-49F2-479F-BFAF-2744184E924A}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -1235,13 +1235,16 @@
       <c r="A61" s="18">
         <v>46233</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="19">
         <v>46234</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="559" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65164B07-49F2-479F-BFAF-2744184E924A}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{165980CE-C56C-4AAD-BD8D-2682C91F4E10}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1140" yWindow="1140" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DWM" sheetId="4" r:id="rId1"/>
@@ -193,9 +193,6 @@
     <t>UI/UX Design(Portal + App)</t>
   </si>
   <si>
-    <t>Planned to start in 3rd Week of July</t>
-  </si>
-  <si>
     <t>Phase 17</t>
   </si>
   <si>
@@ -263,6 +260,9 @@
   </si>
   <si>
     <t>Production Deployment</t>
+  </si>
+  <si>
+    <t>App will be developed after the final submission and testing.</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -416,7 +416,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1243,7 +1242,7 @@
       <c r="A62" s="19">
         <v>46234</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="9" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1624,7 +1623,7 @@
         <v>46249</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>18</v>
@@ -1655,7 +1654,7 @@
         <v>46257</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>18</v>
@@ -1810,13 +1809,13 @@
         <v>46322</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -1824,10 +1823,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
@@ -1855,10 +1854,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
@@ -1886,10 +1885,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
@@ -1914,7 +1913,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="10">
         <f>G21</f>
@@ -1956,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>10</v>
@@ -1976,13 +1975,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -1996,10 +1995,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2013,10 +2012,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
         <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>65</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2030,10 +2029,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" t="s">
         <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>67</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2047,10 +2046,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2064,10 +2063,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
         <v>69</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2081,10 +2080,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2098,10 +2097,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/it_intern_bngroupindia_com/Documents/tradesphere/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/mohini_chaturvedi_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{165980CE-C56C-4AAD-BD8D-2682C91F4E10}"/>
+  <xr:revisionPtr revIDLastSave="566" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9763CD56-BEA7-4361-B970-84D0B99D0101}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>App will be developed after the final submission and testing.</t>
+  </si>
+  <si>
+    <t>merge with order module</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1657,7 @@
         <v>46257</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>18</v>
@@ -1747,7 +1750,7 @@
         <v>46283</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>18</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/mohini_chaturvedi_bngroupindia_com/Documents/tradesphere/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/mohini_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="566" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9763CD56-BEA7-4361-B970-84D0B99D0101}"/>
+  <xr:revisionPtr revIDLastSave="569" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{258276FD-659A-4719-B9DD-9E41BE8CD50C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="75">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -136,9 +136,6 @@
     <t>Phase 7</t>
   </si>
   <si>
-    <t>Beats &amp; Beat Assignment Module</t>
-  </si>
-  <si>
     <t>Phase 8</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>Phase 11</t>
   </si>
   <si>
-    <t>Retailer Feedback Module</t>
-  </si>
-  <si>
     <t>Phase 12</t>
   </si>
   <si>
@@ -265,7 +259,10 @@
     <t>App will be developed after the final submission and testing.</t>
   </si>
   <si>
-    <t>merge with order module</t>
+    <t>File Handling</t>
+  </si>
+  <si>
+    <t>Beats Module</t>
   </si>
 </sst>
 </file>
@@ -485,6 +482,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1516,7 +1517,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D9" s="3">
         <v>6</v>
@@ -1544,10 +1545,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="D10" s="3">
         <v>7</v>
@@ -1575,10 +1576,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
@@ -1606,10 +1607,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="D12" s="3">
         <v>9</v>
@@ -1637,10 +1638,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D13" s="3">
         <v>10</v>
@@ -1657,7 +1658,7 @@
         <v>46257</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="I13" s="12" t="s">
         <v>18</v>
@@ -1668,10 +1669,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
         <v>11</v>
@@ -1699,10 +1700,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" s="3">
         <v>12</v>
@@ -1730,10 +1731,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
@@ -1761,10 +1762,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
@@ -1792,10 +1793,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
@@ -1818,7 +1819,7 @@
         <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
@@ -1826,10 +1827,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
@@ -1857,10 +1858,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
@@ -1888,10 +1889,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
@@ -1916,7 +1917,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C23" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D23" s="10">
         <f>G21</f>
@@ -1958,7 +1959,7 @@
         <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>10</v>
@@ -1978,13 +1979,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
         <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>61</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -1998,10 +1999,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2015,10 +2016,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2032,10 +2033,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2049,10 +2050,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" t="s">
         <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2066,10 +2067,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2083,10 +2084,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2100,10 +2101,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>7</v>

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/mohini_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="569" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{258276FD-659A-4719-B9DD-9E41BE8CD50C}"/>
+  <xr:revisionPtr revIDLastSave="745" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{764CB6D7-7A52-4253-ACE0-B5FA44899EC7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="82">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -263,6 +263,27 @@
   </si>
   <si>
     <t>Beats Module</t>
+  </si>
+  <si>
+    <t>OutletModule</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Target Module</t>
+  </si>
+  <si>
+    <t>Phase 20</t>
+  </si>
+  <si>
+    <t>Phase 21</t>
+  </si>
+  <si>
+    <t>scheme Module</t>
+  </si>
+  <si>
+    <t>Phase 22</t>
   </si>
 </sst>
 </file>
@@ -273,7 +294,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,6 +318,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -380,7 +408,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -416,6 +444,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,10 +516,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1265,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.453125" customWidth="1"/>
@@ -1369,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="G4" s="14">
-        <f t="shared" ref="G4:G21" si="0">E4+F4</f>
+        <f t="shared" ref="G4:G13" si="0">E4+F4</f>
         <v>46198</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -1430,7 +1460,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="8">
-        <f t="shared" ref="E6:E19" si="1">G5+1</f>
+        <f t="shared" ref="E6:E13" si="1">G5+1</f>
         <v>46207</v>
       </c>
       <c r="F6" s="3">
@@ -1627,7 +1657,7 @@
         <v>46249</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>18</v>
@@ -1672,27 +1702,26 @@
         <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="D14" s="3">
         <v>11</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="1"/>
+        <f>G13+1</f>
         <v>46258</v>
       </c>
       <c r="F14" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G14" s="14">
-        <f t="shared" si="0"/>
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -1703,21 +1732,19 @@
         <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3">
         <v>12</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="1"/>
-        <v>46269</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5</v>
+        <v>46266</v>
+      </c>
+      <c r="F15" s="17">
+        <v>7</v>
       </c>
       <c r="G15" s="14">
-        <f t="shared" si="0"/>
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>21</v>
@@ -1734,24 +1761,22 @@
         <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="1"/>
-        <v>46275</v>
-      </c>
-      <c r="F16" s="3">
-        <v>8</v>
+        <v>46274</v>
+      </c>
+      <c r="F16" s="17">
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <f t="shared" si="0"/>
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>18</v>
@@ -1764,25 +1789,23 @@
       <c r="B17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C17" t="s">
-        <v>46</v>
+      <c r="C17" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
       </c>
       <c r="E17" s="8">
-        <f t="shared" si="1"/>
-        <v>46284</v>
-      </c>
-      <c r="F17" s="17">
-        <v>18</v>
+        <v>46277</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <f t="shared" si="0"/>
-        <v>46302</v>
+        <v>46282</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>18</v>
@@ -1796,24 +1819,23 @@
         <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="1"/>
-        <v>46303</v>
-      </c>
-      <c r="F18" s="17">
-        <v>19</v>
+        <f>G17+1</f>
+        <v>46283</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <f t="shared" si="0"/>
-        <v>46322</v>
+        <v>46287</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>18</v>
@@ -1830,24 +1852,23 @@
         <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="1"/>
-        <v>46323</v>
+        <f>G18+1</f>
+        <v>46288</v>
       </c>
       <c r="F19" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="14">
-        <f t="shared" si="0"/>
-        <v>46332</v>
+        <v>46296</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I19" s="12" t="s">
         <v>18</v>
@@ -1860,25 +1881,24 @@
       <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>52</v>
+      <c r="C20" t="s">
+        <v>46</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
       </c>
       <c r="E20" s="8">
         <f>G19+1</f>
-        <v>46333</v>
-      </c>
-      <c r="F20" s="3">
-        <v>9</v>
+        <v>46297</v>
+      </c>
+      <c r="F20" s="17">
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <f t="shared" si="0"/>
-        <v>46342</v>
+        <v>46312</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>18</v>
@@ -1892,43 +1912,135 @@
         <v>53</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
       </c>
       <c r="E21" s="8">
         <f>G20+1</f>
-        <v>46343</v>
-      </c>
-      <c r="F21" s="3">
-        <v>9</v>
+        <v>46313</v>
+      </c>
+      <c r="F21" s="17">
+        <v>15</v>
       </c>
       <c r="G21" s="14">
-        <f t="shared" si="0"/>
-        <v>46352</v>
+        <f>E21+F21</f>
+        <v>46328</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I21" s="12" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3">
+        <v>19</v>
+      </c>
+      <c r="E22" s="8">
+        <f>G21+1</f>
+        <v>46329</v>
+      </c>
+      <c r="F22" s="3">
+        <v>9</v>
+      </c>
+      <c r="G22" s="14">
+        <f>E22+F22</f>
+        <v>46338</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C23" s="3" t="s">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="3">
+        <v>20</v>
+      </c>
+      <c r="E23" s="19">
+        <v>46339</v>
+      </c>
+      <c r="F23" s="3">
+        <v>10</v>
+      </c>
+      <c r="G23" s="19">
+        <v>46349</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="3">
+        <v>21</v>
+      </c>
+      <c r="E24" s="8">
+        <f>G23+1</f>
+        <v>46350</v>
+      </c>
+      <c r="F24" s="3">
+        <v>10</v>
+      </c>
+      <c r="G24" s="19">
+        <v>46360</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C27" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="10">
-        <f>G21</f>
-        <v>46352</v>
-      </c>
+      <c r="D27" s="10">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E28" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:H21">
+  <conditionalFormatting sqref="H3:H24">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>$P$5</formula>
     </cfRule>
@@ -1940,6 +2052,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/DWM.xlsx
+++ b/DWM.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bnagritech1-my.sharepoint.com/personal/mohini_bngroupindia_com/Documents/tradesphere/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="745" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{764CB6D7-7A52-4253-ACE0-B5FA44899EC7}"/>
+  <xr:revisionPtr revIDLastSave="759" documentId="11_F25DC773A252ABDACC1048B9199B6F7E5ADE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F0EFCE-EC64-4515-A1D4-C62B48B96088}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DWM" sheetId="4" r:id="rId1"/>
-    <sheet name="Phases" sheetId="1" r:id="rId2"/>
-    <sheet name="Project Timeline" sheetId="3" r:id="rId3"/>
+    <sheet name="Attendance_Internship" sheetId="5" state="hidden" r:id="rId1"/>
+    <sheet name="DWM" sheetId="4" r:id="rId2"/>
+    <sheet name="Phases" sheetId="1" r:id="rId3"/>
+    <sheet name="Project Timeline" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="84">
   <si>
     <t>Pilot : Tradesphere</t>
   </si>
@@ -55,6 +56,9 @@
     <t>Leave</t>
   </si>
   <si>
+    <t>Daily Work Management</t>
+  </si>
+  <si>
     <t>Tradesphere Project Tracker</t>
   </si>
   <si>
@@ -82,7 +86,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>weekend off included</t>
+    <t>Weekend Off Included</t>
   </si>
   <si>
     <t>Phase 1</t>
@@ -130,12 +134,18 @@
     <t>Phase 6</t>
   </si>
   <si>
-    <t>Promoter Module</t>
+    <t>Promoter / SR Module</t>
+  </si>
+  <si>
+    <t>SR table to be added</t>
   </si>
   <si>
     <t>Phase 7</t>
   </si>
   <si>
+    <t>Beats Module</t>
+  </si>
+  <si>
     <t>Phase 8</t>
   </si>
   <si>
@@ -157,49 +167,76 @@
     <t>Phase 11</t>
   </si>
   <si>
+    <t>File Handling</t>
+  </si>
+  <si>
     <t>Phase 12</t>
   </si>
   <si>
+    <t>OutletModule</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Phase 13</t>
+  </si>
+  <si>
+    <t>Target Module</t>
+  </si>
+  <si>
+    <t>Phase 14</t>
+  </si>
+  <si>
+    <t>scheme Module</t>
+  </si>
+  <si>
+    <t>Phase 15</t>
+  </si>
+  <si>
     <t>Attendance And EOD Module</t>
   </si>
   <si>
-    <t>Phase 13</t>
+    <t>Phase 16</t>
   </si>
   <si>
     <t>Retailer Stock Management</t>
   </si>
   <si>
-    <t>Phase 14</t>
+    <t>App will be developed after the final submission and testing.</t>
+  </si>
+  <si>
+    <t>Phase 17</t>
   </si>
   <si>
     <t>Order Module</t>
   </si>
   <si>
-    <t>Phase 15</t>
+    <t>Phase 18</t>
   </si>
   <si>
     <t>Database Design &amp; Architecture Setup</t>
   </si>
   <si>
-    <t>Phase 16</t>
+    <t>Phase 19</t>
   </si>
   <si>
     <t>UI/UX Design(Portal + App)</t>
   </si>
   <si>
-    <t>Phase 17</t>
+    <t>Phase 20</t>
   </si>
   <si>
     <t>Dashboard &amp; Reporting</t>
   </si>
   <si>
-    <t>Phase 18</t>
+    <t>Phase 21</t>
   </si>
   <si>
     <t>Testing, Bug fixing</t>
   </si>
   <si>
-    <t>Phase 19</t>
+    <t>Phase 22</t>
   </si>
   <si>
     <t>Deployment And Go-live Support</t>
@@ -254,36 +291,6 @@
   </si>
   <si>
     <t>Production Deployment</t>
-  </si>
-  <si>
-    <t>App will be developed after the final submission and testing.</t>
-  </si>
-  <si>
-    <t>File Handling</t>
-  </si>
-  <si>
-    <t>Beats Module</t>
-  </si>
-  <si>
-    <t>OutletModule</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Target Module</t>
-  </si>
-  <si>
-    <t>Phase 20</t>
-  </si>
-  <si>
-    <t>Phase 21</t>
-  </si>
-  <si>
-    <t>scheme Module</t>
-  </si>
-  <si>
-    <t>Phase 22</t>
   </si>
 </sst>
 </file>
@@ -294,7 +301,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,7 +351,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -404,11 +411,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -441,20 +459,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -482,6 +503,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -780,19 +821,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621EF697-7A02-48CB-A30A-BD5ED0677B80}">
   <dimension ref="A1:B62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="14.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="14.45">
       <c r="A2" s="8">
         <v>46174</v>
       </c>
@@ -800,7 +841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="14.45">
       <c r="A3" s="8">
         <v>46175</v>
       </c>
@@ -808,7 +849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="14.45">
       <c r="A4" s="8">
         <v>46176</v>
       </c>
@@ -816,7 +857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="14.45">
       <c r="A5" s="8">
         <v>46177</v>
       </c>
@@ -824,7 +865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="14.45">
       <c r="A6" s="8">
         <v>46178</v>
       </c>
@@ -832,7 +873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="14.45">
       <c r="A7" s="8">
         <v>46179</v>
       </c>
@@ -840,7 +881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="14.45">
       <c r="A8" s="8">
         <v>46180</v>
       </c>
@@ -848,7 +889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="14.45">
       <c r="A9" s="8">
         <v>46181</v>
       </c>
@@ -856,7 +897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="14.45">
       <c r="A10" s="8">
         <v>46182</v>
       </c>
@@ -864,7 +905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="14.45">
       <c r="A11" s="8">
         <v>46183</v>
       </c>
@@ -872,7 +913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="14.45">
       <c r="A12" s="8">
         <v>46184</v>
       </c>
@@ -880,7 +921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="14.45">
       <c r="A13" s="8">
         <v>46185</v>
       </c>
@@ -888,7 +929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="14.45">
       <c r="A14" s="8">
         <v>46186</v>
       </c>
@@ -896,7 +937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="14.45">
       <c r="A15" s="8">
         <v>46187</v>
       </c>
@@ -904,7 +945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="14.45">
       <c r="A16" s="8">
         <v>46188</v>
       </c>
@@ -912,7 +953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="14.45">
       <c r="A17" s="8">
         <v>46189</v>
       </c>
@@ -920,7 +961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="14.45">
       <c r="A18" s="8">
         <v>46190</v>
       </c>
@@ -928,7 +969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="14.45">
       <c r="A19" s="8">
         <v>46191</v>
       </c>
@@ -936,7 +977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="14.45">
       <c r="A20" s="8">
         <v>46192</v>
       </c>
@@ -944,7 +985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="14.45">
       <c r="A21" s="8">
         <v>46193</v>
       </c>
@@ -952,7 +993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="14.45">
       <c r="A22" s="8">
         <v>46194</v>
       </c>
@@ -960,7 +1001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="14.45">
       <c r="A23" s="8">
         <v>46195</v>
       </c>
@@ -968,7 +1009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" ht="14.45">
       <c r="A24" s="8">
         <v>46196</v>
       </c>
@@ -976,7 +1017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" ht="14.45">
       <c r="A25" s="8">
         <v>46197</v>
       </c>
@@ -984,7 +1025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" ht="14.45">
       <c r="A26" s="8">
         <v>46198</v>
       </c>
@@ -992,7 +1033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="14.45">
       <c r="A27" s="8">
         <v>46199</v>
       </c>
@@ -1000,7 +1041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" ht="14.45">
       <c r="A28" s="8">
         <v>46200</v>
       </c>
@@ -1008,7 +1049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" ht="14.45">
       <c r="A29" s="8">
         <v>46201</v>
       </c>
@@ -1016,7 +1057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" ht="14.45">
       <c r="A30" s="8">
         <v>46202</v>
       </c>
@@ -1024,7 +1065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" ht="14.45">
       <c r="A31" s="15">
         <v>46203</v>
       </c>
@@ -1032,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" ht="14.45">
       <c r="A32" s="8">
         <v>46204</v>
       </c>
@@ -1040,7 +1081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="14.45">
       <c r="A33" s="8">
         <v>46205</v>
       </c>
@@ -1048,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="14.45">
       <c r="A34" s="8">
         <v>46206</v>
       </c>
@@ -1056,7 +1097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="14.45">
       <c r="A35" s="8">
         <v>46207</v>
       </c>
@@ -1064,7 +1105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" ht="14.45">
       <c r="A36" s="8">
         <v>46208</v>
       </c>
@@ -1072,7 +1113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="14.45">
       <c r="A37" s="8">
         <v>46209</v>
       </c>
@@ -1080,7 +1121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="14.45">
       <c r="A38" s="8">
         <v>46210</v>
       </c>
@@ -1088,7 +1129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" ht="14.45">
       <c r="A39" s="8">
         <v>46211</v>
       </c>
@@ -1096,7 +1137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" ht="14.45">
       <c r="A40" s="8">
         <v>46212</v>
       </c>
@@ -1104,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" ht="14.45">
       <c r="A41" s="8">
         <v>46213</v>
       </c>
@@ -1112,7 +1153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" ht="14.45">
       <c r="A42" s="8">
         <v>46214</v>
       </c>
@@ -1120,7 +1161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" ht="14.45">
       <c r="A43" s="8">
         <v>46215</v>
       </c>
@@ -1128,7 +1169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" ht="14.45">
       <c r="A44" s="8">
         <v>46216</v>
       </c>
@@ -1136,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" ht="14.45">
       <c r="A45" s="8">
         <v>46217</v>
       </c>
@@ -1144,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" ht="14.45">
       <c r="A46" s="8">
         <v>46218</v>
       </c>
@@ -1152,7 +1193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" ht="14.45">
       <c r="A47" s="8">
         <v>46219</v>
       </c>
@@ -1160,7 +1201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" ht="14.45">
       <c r="A48" s="8">
         <v>46220</v>
       </c>
@@ -1168,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" ht="14.45">
       <c r="A49" s="8">
         <v>46221</v>
       </c>
@@ -1176,7 +1217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" ht="14.45">
       <c r="A50" s="8">
         <v>46222</v>
       </c>
@@ -1184,7 +1225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" ht="14.45">
       <c r="A51" s="8">
         <v>46223</v>
       </c>
@@ -1192,7 +1233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" ht="14.45">
       <c r="A52" s="8">
         <v>46224</v>
       </c>
@@ -1200,7 +1241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" ht="14.45">
       <c r="A53" s="8">
         <v>46225</v>
       </c>
@@ -1208,7 +1249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" ht="14.45">
       <c r="A54" s="8">
         <v>46226</v>
       </c>
@@ -1216,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" ht="14.45">
       <c r="A55" s="8">
         <v>46227</v>
       </c>
@@ -1224,7 +1265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" ht="14.45">
       <c r="A56" s="8">
         <v>46228</v>
       </c>
@@ -1232,7 +1273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" ht="14.45">
       <c r="A57" s="8">
         <v>46229</v>
       </c>
@@ -1240,7 +1281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" ht="14.45">
       <c r="A58" s="8">
         <v>46230</v>
       </c>
@@ -1248,7 +1289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" ht="14.45">
       <c r="A59" s="8">
         <v>46231</v>
       </c>
@@ -1256,7 +1297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" ht="14.45">
       <c r="A60" s="8">
         <v>46232</v>
       </c>
@@ -1264,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" ht="14.45">
       <c r="A61" s="18">
         <v>46233</v>
       </c>
@@ -1272,12 +1313,43 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" ht="14.45">
       <c r="A62" s="19">
         <v>46234</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"WeekOff"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"Present"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0EB679-3C26-4760-A69A-4B3B2033083D}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1293,68 +1365,68 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P28"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="14.453125" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="7" max="8" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B1" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
+      <c r="B1" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:16" ht="29.1">
       <c r="A2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="8">
@@ -1368,25 +1440,25 @@
         <v>46190</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2"/>
       <c r="P3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="3">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1403,24 +1475,24 @@
         <v>46198</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="3">
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -1437,24 +1509,24 @@
         <v>46206</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3">
         <v>3</v>
@@ -1471,21 +1543,21 @@
         <v>46211</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="3">
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3">
         <v>4</v>
@@ -1502,21 +1574,21 @@
         <v>46216</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="3">
         <v>5</v>
@@ -1533,21 +1605,24 @@
         <v>46222</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="3">
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D9" s="3">
         <v>6</v>
@@ -1564,21 +1639,21 @@
         <v>46230</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="3">
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3">
         <v>7</v>
@@ -1595,21 +1670,21 @@
         <v>46236</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
@@ -1626,21 +1701,21 @@
         <v>46241</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3">
         <v>9</v>
@@ -1657,21 +1732,21 @@
         <v>46249</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3">
         <v>10</v>
@@ -1688,21 +1763,21 @@
         <v>46257</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D14" s="3">
         <v>11</v>
@@ -1718,21 +1793,21 @@
         <v>46265</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D15" s="3">
         <v>12</v>
@@ -1747,21 +1822,21 @@
         <v>46273</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D16" s="3">
         <v>13</v>
@@ -1776,21 +1851,21 @@
         <v>46276</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3">
         <v>14</v>
@@ -1805,21 +1880,21 @@
         <v>46282</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3">
         <v>15</v>
@@ -1835,24 +1910,24 @@
         <v>46287</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
@@ -1868,21 +1943,21 @@
         <v>46296</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D20" s="3">
         <v>17</v>
@@ -1898,21 +1973,21 @@
         <v>46312</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D21" s="3">
         <v>18</v>
@@ -1929,81 +2004,82 @@
         <v>46328</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="16">
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="B22" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="16">
         <v>19</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="15">
         <f>G21+1</f>
         <v>46329</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="16">
         <v>9</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="23">
         <f>E22+F22</f>
         <v>46338</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H22" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="3">
         <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>52</v>
+        <v>63</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D23" s="3">
         <v>20</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="22">
         <v>46339</v>
       </c>
       <c r="F23" s="3">
         <v>10</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="22">
         <v>46349</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="21">
+      <c r="H23" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3">
         <v>21</v>
@@ -2015,26 +2091,27 @@
       <c r="F24" s="3">
         <v>10</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="22">
         <v>46360</v>
       </c>
-      <c r="H24" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H24" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D27" s="10">
         <v>46360</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="E28" s="24"/>
+    <row r="28" spans="1:10">
+      <c r="E28" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2056,66 +2133,66 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB1C660-FD22-424D-B761-DA960EAAB43D}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2124,15 +2201,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -2141,15 +2218,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2158,15 +2235,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -2175,15 +2252,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -2192,15 +2269,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D8">
         <v>6</v>
@@ -2209,15 +2286,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <v>7</v>
